--- a/ai_logs/AI_log_MaiHoangDang.xlsx
+++ b/ai_logs/AI_log_MaiHoangDang.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ki_5_Su26\LAB211\Projects\Group\LAb211-Group3\ai_logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ki_5_Su26\LAB211\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A6210A-1E76-4C6D-91E9-28661F383042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3395CE97-F9AC-41B2-BD5A-1CAF655FDB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="304">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>~95</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
   </si>
   <si>
@@ -101,6 +98,27 @@
   </si>
   <si>
     <t>Rapid prototyping &amp; logic review</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>Code generation, debugging, optimizing syntax</t>
+  </si>
+  <si>
+    <t>Rapid prototyping &amp; Bug fixing</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Requirement analysis, architectural design review, edge case simulation</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Deep structural reflection</t>
   </si>
   <si>
     <t>CORE PROMPTS DISTRIBUTION BY DTC COMPONENT</t>
@@ -427,6 +445,108 @@
     <t>src/repository/CacheManager.java; src/repository/ProductRepository.java</t>
   </si>
   <si>
+    <t>ALGORITHM</t>
+  </si>
+  <si>
+    <t>Quản lý phiên bản</t>
+  </si>
+  <si>
+    <t>Thiết kế cơ chế Compare-and-Swap cho Optimistic Lock</t>
+  </si>
+  <si>
+    <t>"Làm thế nào để đảm bảo việc kiểm tra version và cập nhật tồn kho diễn ra an toàn trong mô phỏng bộ nhớ?"</t>
+  </si>
+  <si>
+    <t>Đề xuất đặt toàn bộ thao tác kiểm tra version, trừ kho và tăng version trong khối synchronized(item) để mô phỏng thao tác CAS của CSDL.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Java không có CAS mức CSDL nên cần mô phỏng bằng vùng tới hạn. Reflection: Giải pháp vừa đảm bảo tính nguyên tử vừa phù hợp mục tiêu học thuật của project.</t>
+  </si>
+  <si>
+    <t>FlashSaleItemRepository.java</t>
+  </si>
+  <si>
+    <t>Tích hợp</t>
+  </si>
+  <si>
+    <t>Điều hướng cơ chế khóa trong OrderController</t>
+  </si>
+  <si>
+    <t>"Controller nên quyết định cơ chế lock như thế nào?"</t>
+  </si>
+  <si>
+    <t>Đề xuất tách riêng các phương thức placeOrder tương ứng với từng LockMechanism.</t>
+  </si>
+  <si>
+    <t>Decision: Tách luồng xử lý giúp benchmark công bằng, dễ bảo trì và tránh ảnh hưởng chéo giữa các cơ chế.</t>
+  </si>
+  <si>
+    <t>OrderController.java</t>
+  </si>
+  <si>
+    <t>DESIGN</t>
+  </si>
+  <si>
+    <t>Kiến trúc Simulator</t>
+  </si>
+  <si>
+    <t>Đảm bảo benchmark công bằng</t>
+  </si>
+  <si>
+    <t>"Làm sao để 4 cơ chế lock chạy trong cùng điều kiện?"</t>
+  </si>
+  <si>
+    <t>Sử dụng CountDownLatch kết hợp ExecutorService để tất cả thread khởi chạy đồng thời với cùng tham số.</t>
+  </si>
+  <si>
+    <t>Reflection: Loại bỏ sai lệch do thời điểm khởi động, giúp kết quả TPS và Overselling có giá trị so sánh.</t>
+  </si>
+  <si>
+    <t>SimulatorController.java</t>
+  </si>
+  <si>
+    <t>TESTING</t>
+  </si>
+  <si>
+    <t>Kiểm thử</t>
+  </si>
+  <si>
+    <t>Xác minh transaction log</t>
+  </si>
+  <si>
+    <t>"Cần kiểm tra gì sau khi đặt hàng thành công?"</t>
+  </si>
+  <si>
+    <t>Khuyến nghị assert LockMechanism được ghi đúng trong Transaction.</t>
+  </si>
+  <si>
+    <t>Reflection: Audit log giúp chứng minh cơ chế đồng bộ thực sự đã được sử dụng, không chỉ dựa vào kết quả benchmark.</t>
+  </si>
+  <si>
+    <t>OrderControllerJUnitTest.java</t>
+  </si>
+  <si>
+    <t>REFLECTION</t>
+  </si>
+  <si>
+    <t>Đánh giá rủi ro</t>
+  </si>
+  <si>
+    <t>Ảnh hưởng của NO_LOCK</t>
+  </si>
+  <si>
+    <t>"NO_LOCK có thể gây hiện tượng gì khi tải cao?"</t>
+  </si>
+  <si>
+    <t>Giải thích hiện tượng overselling do race condition và xem đây là baseline để so sánh.</t>
+  </si>
+  <si>
+    <t>Reflection: Giữ NO_LOCK nhằm minh họa lỗi đồng thời trong môi trường thực nghiệm, không phải giải pháp triển khai thực tế.</t>
+  </si>
+  <si>
+    <t>SimulatorView.java</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -619,6 +739,81 @@
     <t>Không biết business constraints</t>
   </si>
   <si>
+    <t>Race Condition</t>
+  </si>
+  <si>
+    <t>Cho rằng đọc dữ liệu trước synchronized luôn an toàn.</t>
+  </si>
+  <si>
+    <t>Vẫn tồn tại khoảng thời gian giữa lúc đọc và lúc lấy được khóa.</t>
+  </si>
+  <si>
+    <t>Phân tích luồng thực thi.</t>
+  </si>
+  <si>
+    <t>Kiểm tra lại version sau khi vào vùng synchronized.</t>
+  </si>
+  <si>
+    <t>Thiếu tài liệu</t>
+  </si>
+  <si>
+    <t>Repository hoàn toàn độc lập.</t>
+  </si>
+  <si>
+    <t>Repository phụ thuộc cache trong RAM, dữ liệu không bền vững khi chương trình dừng.</t>
+  </si>
+  <si>
+    <t>Rà soát kiến trúc.</t>
+  </si>
+  <si>
+    <t>Bổ sung mô tả giới hạn của cache.</t>
+  </si>
+  <si>
+    <t>Thiếu kiểm thử</t>
+  </si>
+  <si>
+    <t>100 thread là đủ cho mọi trường hợp.</t>
+  </si>
+  <si>
+    <t>Các mức contention khác nhau cho kết quả rất khác.</t>
+  </si>
+  <si>
+    <t>Đánh giá benchmark.</t>
+  </si>
+  <si>
+    <t>Bổ sung nhiều kịch bản 10x,100x,1000x.</t>
+  </si>
+  <si>
+    <t>Lỗi ngữ nghĩa</t>
+  </si>
+  <si>
+    <t>Optimistic Lock luôn nhanh nhất vì không blocking.</t>
+  </si>
+  <si>
+    <t>Retry nhiều lần có thể làm TPS giảm mạnh.</t>
+  </si>
+  <si>
+    <t>Đối chiếu kết quả benchmark.</t>
+  </si>
+  <si>
+    <t>Sửa mô tả tài liệu cho chính xác.</t>
+  </si>
+  <si>
+    <t>Lỗi đồng bộ</t>
+  </si>
+  <si>
+    <t>deductStock() tự động là thao tác nguyên tử.</t>
+  </si>
+  <si>
+    <t>Hàm gồm nhiều bước nên chỉ an toàn khi được bảo vệ bằng cơ chế khóa.</t>
+  </si>
+  <si>
+    <t>Đọc mã nguồn.</t>
+  </si>
+  <si>
+    <t>Giữ NO_LOCK chỉ phục vụ mục đích minh họa.</t>
+  </si>
+  <si>
     <t>SELF-ASSESSMENT CHECKLIST (Trước khi nộp)</t>
   </si>
   <si>
@@ -757,25 +952,7 @@
     <t>Giải thích OptimisticLockException và cơ chế Retry khi cập nhật version của CSV.</t>
   </si>
   <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>Code generation, debugging, optimizing syntax</t>
-  </si>
-  <si>
-    <t>Rapid prototyping &amp; Bug fixing</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
-    <t>Requirement analysis, architectural design review, edge case simulation</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Deep structural reflection</t>
+    <t>~130</t>
   </si>
 </sst>
 </file>
@@ -981,14 +1158,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1005,17 +1179,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1037,29 +1200,55 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1365,226 +1554,227 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" style="16" customWidth="1"/>
-    <col min="2" max="2" width="40" style="16" customWidth="1"/>
-    <col min="3" max="3" width="15" style="16" customWidth="1"/>
-    <col min="4" max="4" width="30" style="16" customWidth="1"/>
-    <col min="5" max="6" width="20" style="16" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="16"/>
+    <col min="1" max="1" width="25" style="10" customWidth="1"/>
+    <col min="2" max="2" width="40" style="10" customWidth="1"/>
+    <col min="3" max="3" width="15" style="10" customWidth="1"/>
+    <col min="4" max="4" width="30" style="10" customWidth="1"/>
+    <col min="5" max="6" width="20" style="10" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="13" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="C11" s="14">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C12" s="15">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="20">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="B16" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="C16" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="23" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="B17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="C17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="D17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="16" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>240</v>
+      <c r="B18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>244</v>
+      <c r="A19" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
     </row>
     <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>29</v>
+      <c r="A22" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="25">
+      <c r="A24" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="19">
         <v>3</v>
       </c>
-      <c r="C24" s="26" t="s">
-        <v>31</v>
+      <c r="C24" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="25">
+      <c r="A25" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="19">
         <v>3</v>
       </c>
-      <c r="C25" s="26" t="s">
-        <v>31</v>
+      <c r="C25" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="25">
+      <c r="A26" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="19">
         <v>3</v>
       </c>
-      <c r="C26" s="26" t="s">
-        <v>31</v>
+      <c r="C26" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="25">
+      <c r="A27" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="19">
         <v>7</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>31</v>
+      <c r="C27" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1610,540 +1800,620 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="A1" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+    </row>
+    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="D4" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="165" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
+        <v>4</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26">
+        <v>5</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="D8" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <v>6</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
+        <v>7</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26">
+        <v>8</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26">
+        <v>9</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26">
+        <v>10</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D13" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26">
+        <v>11</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
-        <v>1</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="165" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30">
-        <v>2</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="30" t="s">
+      <c r="D14" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="26">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="180" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30">
-        <v>3</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="180" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30">
-        <v>4</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="30" t="s">
+      <c r="C16" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24">
-        <v>5</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24">
-        <v>6</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="24" t="s">
+      <c r="C17" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="26">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24">
-        <v>7</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
-        <v>8</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24">
-        <v>9</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24">
-        <v>10</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>122</v>
+      <c r="C18" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24">
+      <c r="A19" s="26">
         <v>16</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>127</v>
+      <c r="B19" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="A20" s="26">
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="A21" s="26">
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="A22" s="26">
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="26" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="A23" s="26">
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="A24" s="26">
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="26" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2165,391 +2435,514 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="A2" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>135</v>
+      <c r="A3" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33">
+      <c r="A4" s="25">
         <v>1</v>
       </c>
-      <c r="B4" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>140</v>
+      <c r="B4" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33">
+      <c r="A5" s="25">
         <v>2</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>145</v>
+      <c r="B5" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33">
+      <c r="A6" s="25">
         <v>3</v>
       </c>
-      <c r="B6" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>150</v>
+      <c r="B6" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="25">
         <v>4</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>155</v>
+      <c r="B7" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33">
+      <c r="A8" s="25">
         <v>5</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>159</v>
+      <c r="B8" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33">
+      <c r="A9" s="25">
         <v>6</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>163</v>
+      <c r="B9" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33">
+      <c r="A10" s="25">
         <v>7</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>167</v>
+      <c r="B10" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33">
+      <c r="A11" s="25">
         <v>8</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>171</v>
+      <c r="B11" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33">
+      <c r="A12" s="25">
         <v>9</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>175</v>
+      <c r="B12" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="25">
+        <v>10</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="25">
+        <v>11</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="A15" s="25">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="A16" s="25">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="A17" s="25">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
     </row>
     <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+    </row>
+    <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+    </row>
+    <row r="36" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="27" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>191</v>
-      </c>
+      <c r="B36" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2572,292 +2965,292 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="A1" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
+      <c r="A2" s="39" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
     </row>
     <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>194</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>196</v>
+        <v>260</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>198</v>
+        <v>262</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>201</v>
+      <c r="B6" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>203</v>
+      <c r="B7" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>205</v>
+      <c r="B8" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>207</v>
+      <c r="B9" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>209</v>
+      <c r="B10" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>210</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>196</v>
+        <v>260</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>211</v>
+        <v>262</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>1</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>213</v>
+      <c r="B14" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>2</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>215</v>
+      <c r="B15" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>3</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>217</v>
+      <c r="B16" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="9">
         <v>4</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>219</v>
+      <c r="B17" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>5</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>221</v>
+      <c r="B18" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>222</v>
+      <c r="A20" s="5" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>223</v>
+      <c r="A21" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>224</v>
+      <c r="A22" s="6" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>225</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>226</v>
+      <c r="A26" s="7" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>229</v>
+      <c r="A27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+      <c r="A28" s="9">
         <v>1</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>231</v>
+      <c r="B28" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="9">
         <v>2</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>233</v>
+      <c r="B29" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="9">
         <v>3</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>235</v>
+      <c r="B30" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="9">
         <v>4</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>237</v>
+      <c r="B31" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
